--- a/BL_features.xlsx
+++ b/BL_features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Backup 12.11.2025\LAPTOP (backup 29.08.2022)\ISTRAZIVANJA-TEKUCA\EPILEPTICNI NAPADI\CODE sredjen\ROUND 1\CODE FINAL\PER SIGNAL\CODE FOR GITHUB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0684ED8-08F2-4486-9837-CFC871A61971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CCBF78-E26F-4D3D-8BFF-4DCC2021DB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4452" yWindow="2712" windowWidth="17280" windowHeight="8964" xr2:uid="{D602EF11-A0EC-40A0-89C8-428C9933DAC8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D602EF11-A0EC-40A0-89C8-428C9933DAC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,11 +33,69 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>SVD1</t>
+  </si>
+  <si>
+    <t>SVD2</t>
+  </si>
+  <si>
+    <t>SVD3</t>
+  </si>
+  <si>
+    <t>SVD4</t>
+  </si>
+  <si>
+    <t>BinEn1</t>
+  </si>
+  <si>
+    <t>BinEn2</t>
+  </si>
+  <si>
+    <t>BinEn3</t>
+  </si>
+  <si>
+    <t>BinEn4</t>
+  </si>
+  <si>
+    <t>Skew2</t>
+  </si>
+  <si>
+    <t>Skew3</t>
+  </si>
+  <si>
+    <t>Skew4</t>
+  </si>
+  <si>
+    <t>SVD: maximal singular value computed over 5-s subsegments (1–4); BinEn: binarized entropy; Skew: skewness.</t>
+  </si>
+  <si>
+    <t>Skew1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +123,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -381,45 +444,116 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{269808ED-5B03-4B0F-9196-E77826D9733D}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>105.43661279450903</v>
       </c>
-      <c r="B1">
+      <c r="B2" s="1">
         <v>85.0367146104131</v>
       </c>
-      <c r="C1">
+      <c r="C2" s="1">
         <v>86.407517072210865</v>
       </c>
-      <c r="D1">
+      <c r="D2" s="1">
         <v>127.60904006268957</v>
       </c>
-      <c r="E1">
+      <c r="E2" s="1">
         <v>0.51502443028325295</v>
       </c>
-      <c r="F1">
+      <c r="F2" s="1">
         <v>0.51665930780290314</v>
       </c>
-      <c r="G1">
+      <c r="G2" s="1">
         <v>0.51621644141099798</v>
       </c>
-      <c r="H1">
+      <c r="H2" s="1">
         <v>0.51654812493973867</v>
       </c>
-      <c r="I1">
+      <c r="I2" s="1">
         <v>5.9478865883637544E-2</v>
       </c>
-      <c r="J1">
+      <c r="J2" s="1">
         <v>6.9338349509392661E-2</v>
       </c>
-      <c r="K1">
+      <c r="K2" s="1">
         <v>5.744888267220348E-2</v>
       </c>
-      <c r="L1">
+      <c r="L2" s="1">
         <v>2.287963937823977E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/BL_features.xlsx
+++ b/BL_features.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CCBF78-E26F-4D3D-8BFF-4DCC2021DB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D56462-7775-4A61-9AB9-B09EAB1164FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D602EF11-A0EC-40A0-89C8-428C9933DAC8}"/>
   </bookViews>
@@ -69,10 +69,10 @@
     <t>Skew4</t>
   </si>
   <si>
-    <t>SVD: maximal singular value computed over 5-s subsegments (1–4); BinEn: binarized entropy; Skew: skewness.</t>
-  </si>
-  <si>
     <t>Skew1</t>
+  </si>
+  <si>
+    <t>SVD: maximal singular value computed over 5-s subsegments (1–4); BinEn : binarized entropy over 5-s subsegments (1–4); Skew: skewness over 5-s subsegments (1–4).</t>
   </si>
 </sst>
 </file>
@@ -487,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>8</v>
@@ -553,7 +553,7 @@
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
